--- a/healthcare_forms/043_health_screening_form--healthcare_forms.xlsx
+++ b/healthcare_forms/043_health_screening_form--healthcare_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="23" customWidth="1" min="2" max="2"/>
-    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -525,13 +525,13 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Personal Info</t>
+          <t>What is your name?</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -548,7 +548,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Medical Conditions</t>
+          <t>Do you have any medical conditions?</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -571,7 +571,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Medical Symptoms</t>
+          <t>Please describe any medical symptoms you are experiencing.</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -584,7 +584,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -594,7 +594,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Medical History</t>
+          <t>Do you have any medical history?</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -617,7 +617,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Travel History</t>
+          <t>Have you traveled recently?</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -630,7 +630,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -640,7 +640,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Travel Places</t>
+          <t>Where have you traveled recently?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -663,7 +663,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Travel Duration</t>
+          <t>How long was your recent trip?</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -686,7 +686,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Medical Precautions</t>
+          <t>Do you have any medical precautions?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -704,12 +704,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>medical_precautions_1</t>
+          <t>medical_device</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Medical Precautions</t>
+          <t>Do you have a medical device that requires special care?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -727,12 +727,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>medical_precautions_2</t>
+          <t>medical_procedures</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Medical Precautions</t>
+          <t>Have you had any medical procedures recently?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -750,12 +750,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>medical_history_2</t>
+          <t>medical_allergies</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Medical History</t>
+          <t>Do you have any known allergies?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -768,90 +768,21 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>medical_history_3</t>
+          <t>medical_insurance</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Medical History</t>
+          <t>What is your medical insurance status?</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>medical_history_4</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Medical History</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>medical_history_5</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Medical History</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>medical_history_6</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Medical History</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -868,10 +799,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C23"/>
+  <dimension ref="A1:C15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="31" customWidth="1" min="1" max="1"/>
+    <col width="29" customWidth="1" min="1" max="1"/>
     <col width="6" customWidth="1" min="2" max="2"/>
     <col width="7" customWidth="1" min="3" max="3"/>
   </cols>
@@ -930,7 +861,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>travel_history_choices</t>
+          <t>medical_history_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -947,7 +878,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>travel_history_choices</t>
+          <t>medical_history_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -964,7 +895,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>travel_places_choices</t>
+          <t>travel_history_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -981,7 +912,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>travel_places_choices</t>
+          <t>travel_history_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1032,7 +963,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>medical_precautions_1_choices</t>
+          <t>medical_device_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1049,7 +980,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>medical_precautions_1_choices</t>
+          <t>medical_device_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1066,7 +997,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>medical_precautions_2_choices</t>
+          <t>medical_procedures_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1083,7 +1014,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>medical_precautions_2_choices</t>
+          <t>medical_procedures_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1100,7 +1031,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>medical_history_2_choices</t>
+          <t>medical_allergies_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1117,7 +1048,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>medical_history_2_choices</t>
+          <t>medical_allergies_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1126,142 +1057,6 @@
         </is>
       </c>
       <c r="C15" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>medical_history_3_choices</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>medical_history_3_choices</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>medical_history_4_choices</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>medical_history_4_choices</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>medical_history_5_choices</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>medical_history_5_choices</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>medical_history_6_choices</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>medical_history_6_choices</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
         <is>
           <t>No</t>
         </is>
